--- a/output/roomself_excel/3720.xlsx
+++ b/output/roomself_excel/3720.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,13 +470,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>250464</v>
+        <v>210600</v>
       </c>
       <c r="D2" t="n">
-        <v>4888</v>
+        <v>3832</v>
       </c>
       <c r="E2" t="n">
-        <v>833</v>
+        <v>547</v>
       </c>
       <c r="F2" t="n">
         <v>406</v>
@@ -502,6 +502,28 @@
       </c>
       <c r="F3" t="n">
         <v>36</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>39864</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1660</v>
+      </c>
+      <c r="E4" t="n">
+        <v>286</v>
+      </c>
+      <c r="F4" t="n">
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/3720.xlsx
+++ b/output/roomself_excel/3720.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,62 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
         </is>
       </c>
     </row>
@@ -475,11 +525,49 @@
       <c r="D2" t="n">
         <v>3832</v>
       </c>
-      <c r="E2" t="n">
-        <v>547</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>406</v>
+        <v>378</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>506</v>
+      </c>
+      <c r="J2" t="n">
+        <v>18</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>506</v>
+      </c>
+      <c r="M2" t="n">
+        <v>19</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>64</v>
+      </c>
+      <c r="P2" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -497,12 +585,34 @@
       <c r="D3" t="n">
         <v>1428</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>152</v>
+      </c>
+      <c r="G3" t="n">
+        <v>35</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>205</v>
       </c>
-      <c r="F3" t="n">
+      <c r="J3" t="n">
         <v>36</v>
       </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +629,34 @@
       <c r="D4" t="n">
         <v>1660</v>
       </c>
-      <c r="E4" t="n">
-        <v>286</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>169</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="G4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>151</v>
+      </c>
+      <c r="J4" t="n">
+        <v>22</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/3720.xlsx
+++ b/output/roomself_excel/3720.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +509,26 @@
           <t>ExtWallWidth_4</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -568,6 +588,22 @@
       </c>
       <c r="P2" t="n">
         <v>27</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>154</v>
+      </c>
+      <c r="T2" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="3">
@@ -613,6 +649,10 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -657,6 +697,22 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>95</v>
+      </c>
+      <c r="T4" t="n">
+        <v>22</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
